--- a/public/exports-from-60-with-coowners/11715311.xlsx
+++ b/public/exports-from-60-with-coowners/11715311.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311017829</t>
+          <t xml:space="preserve">311017836</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311123153</t>
+          <t xml:space="preserve">311123156</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">

--- a/public/exports-from-60-with-coowners/11715311.xlsx
+++ b/public/exports-from-60-with-coowners/11715311.xlsx
@@ -8291,7 +8291,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nøjsomhedsvej 30</t>
+          <t xml:space="preserve">Nymøllevej 38</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2060987</t>
+          <t xml:space="preserve">2060298</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -8310,11 +8310,11 @@
         </is>
       </c>
       <c r="J111">
-        <v>360</v>
+        <v>807</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311090351</t>
+          <t xml:space="preserve">311092119</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-01-09</t>
+          <t xml:space="preserve">2025-01-22</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nymøllevej 38</t>
+          <t xml:space="preserve">Rustenborgvej 19A</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2060298</t>
+          <t xml:space="preserve">8864451</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -8385,11 +8385,11 @@
         </is>
       </c>
       <c r="J112">
-        <v>807</v>
+        <v>819</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311092119</t>
+          <t xml:space="preserve">311092129</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rustenborgvej 19A</t>
+          <t xml:space="preserve">Toftebæksvej 11</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864451</t>
+          <t xml:space="preserve">2029421</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -8460,11 +8460,11 @@
         </is>
       </c>
       <c r="J113">
-        <v>819</v>
+        <v>216</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311092129</t>
+          <t xml:space="preserve">311092135</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftebæksvej 11</t>
+          <t xml:space="preserve">Toftebæksvej 38</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029421</t>
+          <t xml:space="preserve">9166452</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -8535,11 +8535,11 @@
         </is>
       </c>
       <c r="J114">
-        <v>216</v>
+        <v>377</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311092135</t>
+          <t xml:space="preserve">311092130</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftebæksvej 38</t>
+          <t xml:space="preserve">Trongårdsvej 58</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -8601,20 +8601,20 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">9166452</t>
+          <t xml:space="preserve">8864449</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J115">
-        <v>377</v>
+        <v>527</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311092130</t>
+          <t xml:space="preserve">311092132</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trongårdsvej 58</t>
+          <t xml:space="preserve">Hjortholmsvej 6</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8676,20 +8676,20 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864449</t>
+          <t xml:space="preserve">2028340</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J116">
-        <v>527</v>
+        <v>339</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311092132</t>
+          <t xml:space="preserve">311095074</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-01-22</t>
+          <t xml:space="preserve">2025-02-11</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjortholmsvej 6</t>
+          <t xml:space="preserve">Kongevejen 49</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028340</t>
+          <t xml:space="preserve">2027995</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -8760,11 +8760,11 @@
         </is>
       </c>
       <c r="J117">
-        <v>339</v>
+        <v>244</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311095074</t>
+          <t xml:space="preserve">311095076</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8816,17 +8816,17 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevejen 49</t>
+          <t xml:space="preserve">Virumgårdsvej 22A</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027995</t>
+          <t xml:space="preserve">2103443</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -8835,11 +8835,11 @@
         </is>
       </c>
       <c r="J118">
-        <v>244</v>
+        <v>690</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311095076</t>
+          <t xml:space="preserve">311096443</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-02-11</t>
+          <t xml:space="preserve">2025-02-19</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Virumgårdsvej 22A</t>
+          <t xml:space="preserve">Virumgårdsvej 22B</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -8901,20 +8901,20 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2103443</t>
+          <t xml:space="preserve">8864754</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J119">
-        <v>690</v>
+        <v>712</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311096443</t>
+          <t xml:space="preserve">311096444</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Virumgårdsvej 22B</t>
+          <t xml:space="preserve">Virumgårdsvej 22C</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -8981,15 +8981,15 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J120">
-        <v>712</v>
+        <v>824</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311096444</t>
+          <t xml:space="preserve">311096445</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Virumgårdsvej 22C</t>
+          <t xml:space="preserve">Virumgårdsvej 2</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -9051,20 +9051,20 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864754</t>
+          <t xml:space="preserve">2103482</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J121">
-        <v>824</v>
+        <v>374</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311096445</t>
+          <t xml:space="preserve">311098179</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-02-19</t>
+          <t xml:space="preserve">2025-03-02</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Virumgårdsvej 2</t>
+          <t xml:space="preserve">Virumvej 35</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2103482</t>
+          <t xml:space="preserve">8864754</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -9135,11 +9135,11 @@
         </is>
       </c>
       <c r="J122">
-        <v>374</v>
+        <v>350</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311098179</t>
+          <t xml:space="preserve">311098180</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9191,17 +9191,17 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Virumvej 35</t>
+          <t xml:space="preserve">Jernbanepladsen 22</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864754</t>
+          <t xml:space="preserve">2030553</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -9210,11 +9210,11 @@
         </is>
       </c>
       <c r="J123">
-        <v>350</v>
+        <v>904</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311098180</t>
+          <t xml:space="preserve">311104767</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-03-02</t>
+          <t xml:space="preserve">2025-04-01</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanepladsen 22</t>
+          <t xml:space="preserve">Jernbanevej 16</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030553</t>
+          <t xml:space="preserve">2030573</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -9285,11 +9285,11 @@
         </is>
       </c>
       <c r="J124">
-        <v>904</v>
+        <v>436</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311104767</t>
+          <t xml:space="preserve">311104762</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanevej 16</t>
+          <t xml:space="preserve">Rustenborgvej 1C</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030573</t>
+          <t xml:space="preserve">2030225</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -9360,11 +9360,11 @@
         </is>
       </c>
       <c r="J125">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311104762</t>
+          <t xml:space="preserve">311104760</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9431,11 +9431,11 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J126">
-        <v>442</v>
+        <v>78</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rustenborgvej 1C</t>
+          <t xml:space="preserve">Rustenborgvej 2A</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -9501,20 +9501,20 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030225</t>
+          <t xml:space="preserve">2030254</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J127">
-        <v>78</v>
+        <v>296</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311104760</t>
+          <t xml:space="preserve">311104759</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rustenborgvej 2A</t>
+          <t xml:space="preserve">Rustenborgvej 3</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030254</t>
+          <t xml:space="preserve">2030252</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -9585,11 +9585,11 @@
         </is>
       </c>
       <c r="J128">
-        <v>296</v>
+        <v>444</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311104759</t>
+          <t xml:space="preserve">311104755</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rustenborgvej 3</t>
+          <t xml:space="preserve">Nørregade 9</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -9651,20 +9651,20 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030252</t>
+          <t xml:space="preserve">8864425</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J129">
-        <v>444</v>
+        <v>235</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311104755</t>
+          <t xml:space="preserve">311107482</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-01</t>
+          <t xml:space="preserve">2025-04-17</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9731,15 +9731,15 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J130">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311107482</t>
+          <t xml:space="preserve">311107735</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-17</t>
+          <t xml:space="preserve">2025-04-20</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9806,11 +9806,11 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J131">
-        <v>265</v>
+        <v>224</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 9</t>
+          <t xml:space="preserve">Sorgenfrivej 13</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -9876,20 +9876,20 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864425</t>
+          <t xml:space="preserve">2029916</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J132">
-        <v>224</v>
+        <v>502</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311107735</t>
+          <t xml:space="preserve">311107784</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sorgenfrivej 13</t>
+          <t xml:space="preserve">Nørregade 14</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9951,20 +9951,20 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029916</t>
+          <t xml:space="preserve">8864425</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J133">
-        <v>502</v>
+        <v>202</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311107784</t>
+          <t xml:space="preserve">311108491</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-20</t>
+          <t xml:space="preserve">2025-04-23</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -10031,11 +10031,11 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J134">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
@@ -10091,40 +10091,40 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 14</t>
+          <t xml:space="preserve">Taarbæk Strandvej 84</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2930</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864425</t>
+          <t xml:space="preserve">2047087</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J135">
-        <v>198</v>
+        <v>545</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311108491</t>
+          <t xml:space="preserve">311123153</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning Aps</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-23</t>
+          <t xml:space="preserve">2025-07-03</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10166,40 +10166,40 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taarbæk Strandvej 84</t>
+          <t xml:space="preserve">Hasselvej 74B</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2047087</t>
+          <t xml:space="preserve">1301698</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J136">
-        <v>545</v>
+        <v>298</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311123156</t>
+          <t xml:space="preserve">311136466</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning Aps</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-03</t>
+          <t xml:space="preserve">2025-09-24</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10256,15 +10256,15 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J137">
-        <v>298</v>
+        <v>355</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311136466</t>
+          <t xml:space="preserve">311136474</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10316,40 +10316,40 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hasselvej 74B</t>
+          <t xml:space="preserve">Lundtoftevej 53A</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301698</t>
+          <t xml:space="preserve">8864426</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="J138">
-        <v>355</v>
+        <v>846</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311136474</t>
+          <t xml:space="preserve">311139246</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning Aps</t>
+          <t xml:space="preserve">JDM Rådgivende Ingeniør ApS</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-24</t>
+          <t xml:space="preserve">2025-10-09</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 53A</t>
+          <t xml:space="preserve">Lundtoftevej 53C</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -10401,16 +10401,16 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864426</t>
+          <t xml:space="preserve">715219, 8864426</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="J139">
-        <v>846</v>
+        <v>135</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 53C</t>
+          <t xml:space="preserve">Buddingevej 39</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -10476,30 +10476,30 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">715219, 8864426</t>
+          <t xml:space="preserve">2064573</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J140">
-        <v>135</v>
+        <v>334</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311139246</t>
+          <t xml:space="preserve">311145808</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t xml:space="preserve">JDM Rådgivende Ingeniør ApS</t>
+          <t xml:space="preserve">TRANEKAER-ARKITEKTKONTOR.DK aps</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-09</t>
+          <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10541,40 +10541,40 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buddingevej 39</t>
+          <t xml:space="preserve">Askevænget 10</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2064573</t>
+          <t xml:space="preserve">1301698</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J141">
-        <v>334</v>
+        <v>1060</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145808</t>
+          <t xml:space="preserve">311150499</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRANEKAER-ARKITEKTKONTOR.DK aps</t>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-17</t>
+          <t xml:space="preserve">2025-12-16</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10616,30 +10616,30 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Askevænget 10</t>
+          <t xml:space="preserve">Nøjsomhedsvej 11</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301698</t>
+          <t xml:space="preserve">2061486</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J142">
-        <v>1060</v>
+        <v>634</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311150499</t>
+          <t xml:space="preserve">311176540</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-16</t>
+          <t xml:space="preserve">2026-05-13</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nøjsomhedsvej 11</t>
+          <t xml:space="preserve">Lyngby Torv 16</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -10701,20 +10701,20 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2061486</t>
+          <t xml:space="preserve">2030182</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J143">
-        <v>634</v>
+        <v>266</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311176540</t>
+          <t xml:space="preserve">311179524</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-13</t>
+          <t xml:space="preserve">2026-05-30</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby Torv 16</t>
+          <t xml:space="preserve">Hjortholmsvej 3</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030182</t>
+          <t xml:space="preserve">2028337</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -10785,11 +10785,11 @@
         </is>
       </c>
       <c r="J144">
-        <v>266</v>
+        <v>356</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311179524</t>
+          <t xml:space="preserve">311195275</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-30</t>
+          <t xml:space="preserve">2026-08-18</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10841,30 +10841,30 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjortholmsvej 3</t>
+          <t xml:space="preserve">Kongsvænget 10C</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028337</t>
+          <t xml:space="preserve">2030815</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J145">
-        <v>356</v>
+        <v>853</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311195275</t>
+          <t xml:space="preserve">311196141</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-18</t>
+          <t xml:space="preserve">2026-08-23</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongsvænget 10C</t>
+          <t xml:space="preserve">Grønnevej 218</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -10926,20 +10926,20 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030815</t>
+          <t xml:space="preserve">2103430</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J146">
-        <v>853</v>
+        <v>813</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311196141</t>
+          <t xml:space="preserve">311198636</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-23</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10986,55 +10986,55 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">173</t>
+          <t xml:space="preserve">190</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnevej 218</t>
+          <t xml:space="preserve">Lejrvej 47</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2103430</t>
+          <t xml:space="preserve">2134936</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J147">
-        <v>813</v>
+        <v>636</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311198636</t>
+          <t xml:space="preserve">311231307</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+          <t xml:space="preserve">Energitjenesten Øst</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2027-02-08</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -11061,45 +11061,45 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">190</t>
+          <t xml:space="preserve">173</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lejrvej 47</t>
+          <t xml:space="preserve">Christian X's Alle 95C</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2134936</t>
+          <t xml:space="preserve">206570</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J148">
-        <v>636</v>
+        <v>300</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231307</t>
+          <t xml:space="preserve">311230119</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energitjenesten Øst</t>
+          <t xml:space="preserve">Arkitektfirmaet Byg &amp; Bo ApS</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-08</t>
+          <t xml:space="preserve">2027-02-23</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian X's Alle 95C</t>
+          <t xml:space="preserve">Christian X's Alle 95D</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J149">
@@ -11164,7 +11164,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230119</t>
+          <t xml:space="preserve">311230118</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian X's Alle 95D</t>
+          <t xml:space="preserve">Christian X's Alle 95E</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -11231,15 +11231,15 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J150">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230118</t>
+          <t xml:space="preserve">311230107</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11291,40 +11291,40 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian X's Alle 95E</t>
+          <t xml:space="preserve">Strandvejen 607</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2930</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">206570</t>
+          <t xml:space="preserve">2047266</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J151">
-        <v>450</v>
+        <v>148</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230107</t>
+          <t xml:space="preserve">311233876</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arkitektfirmaet Byg &amp; Bo ApS</t>
+          <t xml:space="preserve">Møllevang Tegnestue</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-23</t>
+          <t xml:space="preserve">2027-03-13</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11366,40 +11366,40 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 607</t>
+          <t xml:space="preserve">Engelsborgvej 66</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2047266</t>
+          <t xml:space="preserve">1301455</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J152">
-        <v>148</v>
+        <v>1774</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233876</t>
+          <t xml:space="preserve">311245601</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevang Tegnestue</t>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-13</t>
+          <t xml:space="preserve">2027-05-05</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11451,20 +11451,20 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301455</t>
+          <t xml:space="preserve">2064948</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J153">
-        <v>1774</v>
+        <v>680</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311245601</t>
+          <t xml:space="preserve">311245596</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11531,15 +11531,15 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J154">
-        <v>680</v>
+        <v>1946</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311245596</t>
+          <t xml:space="preserve">311245602</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engelsborgvej 66</t>
+          <t xml:space="preserve">Toftebæksvej 8</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -11601,20 +11601,20 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2064948</t>
+          <t xml:space="preserve">8864411</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J155">
-        <v>1946</v>
+        <v>942</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311245602</t>
+          <t xml:space="preserve">311251199</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-05</t>
+          <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftebæksvej 8</t>
+          <t xml:space="preserve">Ravnholmvej 7</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864411</t>
+          <t xml:space="preserve">2062047</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -11685,11 +11685,11 @@
         </is>
       </c>
       <c r="J156">
-        <v>942</v>
+        <v>266</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251199</t>
+          <t xml:space="preserve">311290836</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-01</t>
+          <t xml:space="preserve">2028-01-02</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11741,17 +11741,17 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnholmvej 7</t>
+          <t xml:space="preserve">Taarbæk Strandvej 90</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2930</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2062047</t>
+          <t xml:space="preserve">2047232</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -11760,11 +11760,11 @@
         </is>
       </c>
       <c r="J157">
-        <v>266</v>
+        <v>295</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290836</t>
+          <t xml:space="preserve">311290924</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-02</t>
+          <t xml:space="preserve">2028-01-03</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11816,17 +11816,17 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taarbæk Strandvej 90</t>
+          <t xml:space="preserve">Caroline Amalie Vej 118</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2047232</t>
+          <t xml:space="preserve">8864558</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -11835,11 +11835,11 @@
         </is>
       </c>
       <c r="J158">
-        <v>295</v>
+        <v>864</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290924</t>
+          <t xml:space="preserve">311295408</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-03</t>
+          <t xml:space="preserve">2028-01-31</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caroline Amalie Vej 118</t>
+          <t xml:space="preserve">Caroline Amalie Vej 120</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J159">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311295408</t>
+          <t xml:space="preserve">311295440</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caroline Amalie Vej 120</t>
+          <t xml:space="preserve">Caroline Amalie Vej 122</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -11981,15 +11981,15 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J160">
-        <v>864</v>
+        <v>969</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311295440</t>
+          <t xml:space="preserve">311295444</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caroline Amalie Vej 122</t>
+          <t xml:space="preserve">Caroline Amalie Vej 124</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12056,15 +12056,15 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J161">
-        <v>969</v>
+        <v>658</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311295444</t>
+          <t xml:space="preserve">311295460</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caroline Amalie Vej 124</t>
+          <t xml:space="preserve">Caroline Amalie Vej 126</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -12131,15 +12131,15 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J162">
-        <v>658</v>
+        <v>3833</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311295460</t>
+          <t xml:space="preserve">311295495</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caroline Amalie Vej 126</t>
+          <t xml:space="preserve">Jægersborgvej 19</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -12201,20 +12201,20 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864558</t>
+          <t xml:space="preserve">2028514</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J163">
-        <v>3833</v>
+        <v>232</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311295495</t>
+          <t xml:space="preserve">311297484</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-31</t>
+          <t xml:space="preserve">2028-02-13</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jægersborgvej 19</t>
+          <t xml:space="preserve">Lyngby Hovedgade 102A</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028514</t>
+          <t xml:space="preserve">2065603</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -12285,11 +12285,11 @@
         </is>
       </c>
       <c r="J164">
-        <v>232</v>
+        <v>2277</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311297484</t>
+          <t xml:space="preserve">311298110</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-13</t>
+          <t xml:space="preserve">2028-02-16</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby Hovedgade 102A</t>
+          <t xml:space="preserve">Christian X's Alle 97A</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -12351,20 +12351,20 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2065603</t>
+          <t xml:space="preserve">100497999</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J165">
-        <v>2277</v>
+        <v>280</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311298110</t>
+          <t xml:space="preserve">311306901</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-16</t>
+          <t xml:space="preserve">2028-04-06</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian X's Alle 97A</t>
+          <t xml:space="preserve">Sorgenfrigårdsvej 37</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12426,20 +12426,20 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">100497999</t>
+          <t xml:space="preserve">2029392</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J166">
-        <v>280</v>
+        <v>317</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306901</t>
+          <t xml:space="preserve">311313170</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-06</t>
+          <t xml:space="preserve">2028-05-09</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sorgenfrigårdsvej 37</t>
+          <t xml:space="preserve">Fuglevadsvej 49</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029392</t>
+          <t xml:space="preserve">1300682</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -12510,11 +12510,11 @@
         </is>
       </c>
       <c r="J167">
-        <v>317</v>
+        <v>1035</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311313170</t>
+          <t xml:space="preserve">311315069</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-09</t>
+          <t xml:space="preserve">2028-05-18</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglevadsvej 49</t>
+          <t xml:space="preserve">Lundtofte Skolestr. 7</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -12576,20 +12576,20 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300682</t>
+          <t xml:space="preserve">2060774</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J168">
-        <v>1035</v>
+        <v>148</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311315069</t>
+          <t xml:space="preserve">311317367</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-18</t>
+          <t xml:space="preserve">2028-05-30</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtofte Skolestr. 7</t>
+          <t xml:space="preserve">Ravnholmvej 11</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -12656,11 +12656,11 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J169">
-        <v>148</v>
+        <v>2508</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnholmvej 11</t>
+          <t xml:space="preserve">Kulsviervej 5</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -12726,30 +12726,30 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2060774</t>
+          <t xml:space="preserve">2062257</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J170">
-        <v>2508</v>
+        <v>264</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311317367</t>
+          <t xml:space="preserve">311319303</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-30</t>
+          <t xml:space="preserve">2028-06-08</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kulsviervej 5</t>
+          <t xml:space="preserve">Toftebæksvej 17</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -12801,25 +12801,25 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2062257</t>
+          <t xml:space="preserve">8864437</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J171">
-        <v>264</v>
+        <v>850</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319303</t>
+          <t xml:space="preserve">311319296</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -12866,17 +12866,17 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftebæksvej 17</t>
+          <t xml:space="preserve">Grønnevej 218</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864437</t>
+          <t xml:space="preserve">2103430</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -12885,11 +12885,11 @@
         </is>
       </c>
       <c r="J172">
-        <v>850</v>
+        <v>3585</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319296</t>
+          <t xml:space="preserve">311324386</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -12899,7 +12899,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-08</t>
+          <t xml:space="preserve">2028-07-03</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12956,15 +12956,15 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J173">
-        <v>3585</v>
+        <v>640</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324386</t>
+          <t xml:space="preserve">311324387</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -13031,15 +13031,15 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J174">
-        <v>640</v>
+        <v>1326</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324387</t>
+          <t xml:space="preserve">311324386</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnevej 218</t>
+          <t xml:space="preserve">Geels Plads 40</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -13101,20 +13101,20 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2103430</t>
+          <t xml:space="preserve">2074600</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J175">
-        <v>1326</v>
+        <v>3579</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324386</t>
+          <t xml:space="preserve">311330677</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-07-03</t>
+          <t xml:space="preserve">2028-08-15</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -13166,30 +13166,30 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Geels Plads 40</t>
+          <t xml:space="preserve">Trongårdsvej 50</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2074600</t>
+          <t xml:space="preserve">8864449</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J176">
-        <v>3579</v>
+        <v>986</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311330677</t>
+          <t xml:space="preserve">311330689</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trongårdsvej 50</t>
+          <t xml:space="preserve">Trongårdsvej 60</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -13256,15 +13256,15 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J177">
-        <v>986</v>
+        <v>130</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311330689</t>
+          <t xml:space="preserve">311330692</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trongårdsvej 60</t>
+          <t xml:space="preserve">Trongårdsvej 50</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -13331,15 +13331,15 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J178">
-        <v>130</v>
+        <v>6598</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311330692</t>
+          <t xml:space="preserve">311331058</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-15</t>
+          <t xml:space="preserve">2028-08-17</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trongårdsvej 50</t>
+          <t xml:space="preserve">Kongevejen 55</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -13401,20 +13401,20 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864449</t>
+          <t xml:space="preserve">2028010</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J179">
-        <v>6598</v>
+        <v>1575</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311331058</t>
+          <t xml:space="preserve">311333738</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-17</t>
+          <t xml:space="preserve">2028-08-31</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13481,11 +13481,11 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J180">
-        <v>1575</v>
+        <v>370</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevejen 55</t>
+          <t xml:space="preserve">Kongevejen 57</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -13556,11 +13556,11 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J181">
-        <v>370</v>
+        <v>535</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevejen 57</t>
+          <t xml:space="preserve">Lyngbygårdsvej 37</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028010</t>
+          <t xml:space="preserve">2029334</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -13635,21 +13635,21 @@
         </is>
       </c>
       <c r="J182">
-        <v>535</v>
+        <v>6394</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311333738</t>
+          <t xml:space="preserve">311336039</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-31</t>
+          <t xml:space="preserve">2028-09-13</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13706,11 +13706,11 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J183">
-        <v>6394</v>
+        <v>503</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
@@ -13781,20 +13781,20 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J184">
-        <v>503</v>
+        <v>205</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311336039</t>
+          <t xml:space="preserve">311336048</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -13841,17 +13841,17 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngbygårdsvej 37</t>
+          <t xml:space="preserve">Kongsvænget 10</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029334</t>
+          <t xml:space="preserve">2030815</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -13860,11 +13860,11 @@
         </is>
       </c>
       <c r="J185">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311336048</t>
+          <t xml:space="preserve">311336291</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-13</t>
+          <t xml:space="preserve">2028-09-14</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongsvænget 10</t>
+          <t xml:space="preserve">Kongsvænget 10B</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -13931,11 +13931,11 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J186">
-        <v>3540</v>
+        <v>2552</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
@@ -13991,30 +13991,30 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongsvænget 10</t>
+          <t xml:space="preserve">Lyngby Hovedgade 28</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030815</t>
+          <t xml:space="preserve">2030466</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J187">
-        <v>428</v>
+        <v>4499</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311336294</t>
+          <t xml:space="preserve">311337951</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-14</t>
+          <t xml:space="preserve">2028-09-25</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -14066,40 +14066,40 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongsvænget 10</t>
+          <t xml:space="preserve">Nybrovej 401B</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030815</t>
+          <t xml:space="preserve">8864737</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J188">
-        <v>431</v>
+        <v>497</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311336294</t>
+          <t xml:space="preserve">311339703</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-14</t>
+          <t xml:space="preserve">2028-10-04</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -14141,17 +14141,17 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongsvænget 10</t>
+          <t xml:space="preserve">Nybrovej 401C</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030815</t>
+          <t xml:space="preserve">8864737</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -14160,21 +14160,21 @@
         </is>
       </c>
       <c r="J189">
-        <v>235</v>
+        <v>100</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311336291</t>
+          <t xml:space="preserve">311339704</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-14</t>
+          <t xml:space="preserve">2028-10-04</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -14216,40 +14216,40 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongsvænget 10B</t>
+          <t xml:space="preserve">Becksvej 3</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2930</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030815</t>
+          <t xml:space="preserve">2047221</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J190">
-        <v>2552</v>
+        <v>327</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311336294</t>
+          <t xml:space="preserve">311345047</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-14</t>
+          <t xml:space="preserve">2028-11-05</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby Hovedgade 28</t>
+          <t xml:space="preserve">Lyngby Hovedgade 1A</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -14301,7 +14301,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030466</t>
+          <t xml:space="preserve">203119</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -14310,21 +14310,21 @@
         </is>
       </c>
       <c r="J191">
-        <v>4499</v>
+        <v>3922</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311337951</t>
+          <t xml:space="preserve">311345064</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-25</t>
+          <t xml:space="preserve">2028-11-05</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -14366,30 +14366,30 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 401B</t>
+          <t xml:space="preserve">Taarbæk Strandvej 96A</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2930</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864737</t>
+          <t xml:space="preserve">2047221</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J192">
-        <v>497</v>
+        <v>2624</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311339703</t>
+          <t xml:space="preserve">311345057</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -14399,7 +14399,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-04</t>
+          <t xml:space="preserve">2028-11-05</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 401C</t>
+          <t xml:space="preserve">Bauneporten 20</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -14451,20 +14451,20 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864737</t>
+          <t xml:space="preserve">2029353</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J193">
-        <v>100</v>
+        <v>3101</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311339704</t>
+          <t xml:space="preserve">311346074</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-04</t>
+          <t xml:space="preserve">2028-11-09</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14516,17 +14516,17 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Becksvej 3</t>
+          <t xml:space="preserve">Parcelvej 151</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2047221</t>
+          <t xml:space="preserve">8139785</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -14535,21 +14535,21 @@
         </is>
       </c>
       <c r="J194">
-        <v>327</v>
+        <v>136</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311345047</t>
+          <t xml:space="preserve">311353958</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-05</t>
+          <t xml:space="preserve">2029-01-09</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14591,40 +14591,40 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby Hovedgade 1A</t>
+          <t xml:space="preserve">Parcelvej 151</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">203119</t>
+          <t xml:space="preserve">8139785</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J195">
-        <v>3922</v>
+        <v>160</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311345064</t>
+          <t xml:space="preserve">311353958</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-05</t>
+          <t xml:space="preserve">2029-01-09</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14666,17 +14666,17 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taarbæk Strandvej 96A</t>
+          <t xml:space="preserve">Parcelvej 153</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2047221</t>
+          <t xml:space="preserve">8139785</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -14685,21 +14685,21 @@
         </is>
       </c>
       <c r="J196">
-        <v>2624</v>
+        <v>148</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311345057</t>
+          <t xml:space="preserve">311353958</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-05</t>
+          <t xml:space="preserve">2029-01-09</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14741,40 +14741,40 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bauneporten 20</t>
+          <t xml:space="preserve">Skolebakken 9</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029353</t>
+          <t xml:space="preserve">8139785</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J197">
-        <v>3101</v>
+        <v>16483</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311346074</t>
+          <t xml:space="preserve">311353958</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-09</t>
+          <t xml:space="preserve">2029-01-09</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14816,40 +14816,40 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parcelvej 151</t>
+          <t xml:space="preserve">Lundtoftevej 53A</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">8139785</t>
+          <t xml:space="preserve">8864426</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J198">
-        <v>136</v>
+        <v>4637</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311353958</t>
+          <t xml:space="preserve">311361942</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-09</t>
+          <t xml:space="preserve">2029-02-28</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14891,40 +14891,40 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parcelvej 151</t>
+          <t xml:space="preserve">Lundtoftevej 53A</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">8139785</t>
+          <t xml:space="preserve">8864426</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J199">
-        <v>160</v>
+        <v>3693</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311353958</t>
+          <t xml:space="preserve">311361942</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-09</t>
+          <t xml:space="preserve">2029-02-28</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14966,40 +14966,40 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parcelvej 153</t>
+          <t xml:space="preserve">Lundtoftevej 53A</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">8139785</t>
+          <t xml:space="preserve">8864426</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J200">
-        <v>148</v>
+        <v>1405</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311353958</t>
+          <t xml:space="preserve">311361942</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-09</t>
+          <t xml:space="preserve">2029-02-28</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -15041,40 +15041,40 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 9</t>
+          <t xml:space="preserve">Lundtoftevej 53A</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">8139785</t>
+          <t xml:space="preserve">8864426</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J201">
-        <v>16483</v>
+        <v>3674</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311353958</t>
+          <t xml:space="preserve">311361942</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-09</t>
+          <t xml:space="preserve">2029-02-28</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 53A</t>
+          <t xml:space="preserve">Gyrithe Lemches Vej 14</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -15131,15 +15131,15 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="J202">
-        <v>4637</v>
+        <v>908</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311361942</t>
+          <t xml:space="preserve">311362217</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-28</t>
+          <t xml:space="preserve">2029-03-01</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 53A</t>
+          <t xml:space="preserve">Christian X's Alle 95A</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -15201,20 +15201,20 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864426</t>
+          <t xml:space="preserve">206570</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J203">
-        <v>3693</v>
+        <v>1790</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311361942</t>
+          <t xml:space="preserve">311367421</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-28</t>
+          <t xml:space="preserve">2029-03-27</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -15266,7 +15266,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 53A</t>
+          <t xml:space="preserve">Christian X's Alle 95B</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -15276,20 +15276,20 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864426</t>
+          <t xml:space="preserve">206568, 206569</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J204">
-        <v>1405</v>
+        <v>782</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311361942</t>
+          <t xml:space="preserve">311367239</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-28</t>
+          <t xml:space="preserve">2029-03-27</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -15341,30 +15341,30 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 53A</t>
+          <t xml:space="preserve">Biskop Monrads Vej 15</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864426</t>
+          <t xml:space="preserve">2102160</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J205">
-        <v>3674</v>
+        <v>164</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311361942</t>
+          <t xml:space="preserve">311481405</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -15374,7 +15374,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-28</t>
+          <t xml:space="preserve">2030-12-08</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyrithe Lemches Vej 14</t>
+          <t xml:space="preserve">Christian X's Alle 113</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -15426,30 +15426,30 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864426</t>
+          <t xml:space="preserve">1301456</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J206">
-        <v>908</v>
+        <v>266</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311362217</t>
+          <t xml:space="preserve">311481297</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-01</t>
+          <t xml:space="preserve">2030-12-08</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -15491,7 +15491,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian X's Alle 95A</t>
+          <t xml:space="preserve">Gasværksvej 10</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -15501,7 +15501,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">206570</t>
+          <t xml:space="preserve">2028305</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -15510,11 +15510,11 @@
         </is>
       </c>
       <c r="J207">
-        <v>1790</v>
+        <v>194</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311367421</t>
+          <t xml:space="preserve">311481418</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -15524,7 +15524,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-27</t>
+          <t xml:space="preserve">2030-12-08</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -15566,7 +15566,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian X's Alle 95B</t>
+          <t xml:space="preserve">Kulsviervej 115</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -15576,20 +15576,20 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">206568, 206569</t>
+          <t xml:space="preserve">2060251</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J208">
-        <v>782</v>
+        <v>470</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311367239</t>
+          <t xml:space="preserve">311481296</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-27</t>
+          <t xml:space="preserve">2030-12-08</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15641,30 +15641,30 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biskop Monrads Vej 15</t>
+          <t xml:space="preserve">Lundtoftevej 212</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2102160</t>
+          <t xml:space="preserve">2061449</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J209">
-        <v>164</v>
+        <v>263</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481405</t>
+          <t xml:space="preserve">311481407</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian X's Alle 113</t>
+          <t xml:space="preserve">Lundtoftevej 218</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301456</t>
+          <t xml:space="preserve">8864537</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -15735,16 +15735,16 @@
         </is>
       </c>
       <c r="J210">
-        <v>266</v>
+        <v>174</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481297</t>
+          <t xml:space="preserve">311481412</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasværksvej 10</t>
+          <t xml:space="preserve">Lyngby Hovedgade 70C</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -15801,7 +15801,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028305</t>
+          <t xml:space="preserve">100052, 100053, 100054, 100055</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -15810,11 +15810,11 @@
         </is>
       </c>
       <c r="J211">
-        <v>194</v>
+        <v>432</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481418</t>
+          <t xml:space="preserve">311481300</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -15866,7 +15866,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kulsviervej 115</t>
+          <t xml:space="preserve">Nybrovej 457</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -15876,7 +15876,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2060251</t>
+          <t xml:space="preserve">2102136</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -15885,11 +15885,11 @@
         </is>
       </c>
       <c r="J212">
-        <v>470</v>
+        <v>185</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481296</t>
+          <t xml:space="preserve">311481385</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -15941,17 +15941,17 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 212</t>
+          <t xml:space="preserve">Virumvej 121</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2061449</t>
+          <t xml:space="preserve">2077301</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -15960,11 +15960,11 @@
         </is>
       </c>
       <c r="J213">
-        <v>263</v>
+        <v>185</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481407</t>
+          <t xml:space="preserve">311481298</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -16016,7 +16016,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 218</t>
+          <t xml:space="preserve">Lottenborgvej 16</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -16026,7 +16026,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864537</t>
+          <t xml:space="preserve">2028027</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -16035,11 +16035,11 @@
         </is>
       </c>
       <c r="J214">
-        <v>174</v>
+        <v>91</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481412</t>
+          <t xml:space="preserve">311484955</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16049,7 +16049,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-08</t>
+          <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -16091,7 +16091,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby Hovedgade 70C</t>
+          <t xml:space="preserve">Lottenborgvej 16</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -16101,20 +16101,20 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052, 100053, 100054, 100055</t>
+          <t xml:space="preserve">2028027</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J215">
-        <v>432</v>
+        <v>121</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481300</t>
+          <t xml:space="preserve">311484954</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -16124,7 +16124,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-08</t>
+          <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -16166,7 +16166,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 457</t>
+          <t xml:space="preserve">Lundtoftevej 51A</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -16176,7 +16176,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2102136</t>
+          <t xml:space="preserve">2029203</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -16185,11 +16185,11 @@
         </is>
       </c>
       <c r="J216">
-        <v>185</v>
+        <v>214</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481385</t>
+          <t xml:space="preserve">311485502</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -16199,7 +16199,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-08</t>
+          <t xml:space="preserve">2031-01-04</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -16241,17 +16241,17 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Virumvej 121</t>
+          <t xml:space="preserve">Lundtoftevej 55A</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2077301</t>
+          <t xml:space="preserve">2029204</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -16260,11 +16260,11 @@
         </is>
       </c>
       <c r="J217">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481298</t>
+          <t xml:space="preserve">311485503</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -16274,7 +16274,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-08</t>
+          <t xml:space="preserve">2031-01-04</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lottenborgvej 16</t>
+          <t xml:space="preserve">Lundtoftevej 57A</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -16326,7 +16326,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028027</t>
+          <t xml:space="preserve">2029205</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -16335,11 +16335,11 @@
         </is>
       </c>
       <c r="J218">
-        <v>91</v>
+        <v>214</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484955</t>
+          <t xml:space="preserve">311485504</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -16349,7 +16349,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-23</t>
+          <t xml:space="preserve">2031-01-04</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lottenborgvej 16</t>
+          <t xml:space="preserve">Lundtoftevej 59A</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -16401,20 +16401,20 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028027</t>
+          <t xml:space="preserve">2029206</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J219">
-        <v>121</v>
+        <v>214</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484954</t>
+          <t xml:space="preserve">311485505</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-23</t>
+          <t xml:space="preserve">2031-01-04</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -16466,7 +16466,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 51A</t>
+          <t xml:space="preserve">Gammel Lundtoftevej 6</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -16476,7 +16476,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029203</t>
+          <t xml:space="preserve">2030472</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -16485,11 +16485,11 @@
         </is>
       </c>
       <c r="J220">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485502</t>
+          <t xml:space="preserve">311520616</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-04</t>
+          <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -16541,7 +16541,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 55A</t>
+          <t xml:space="preserve">Lyngby Hovedgade 1C</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -16551,7 +16551,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029204</t>
+          <t xml:space="preserve">100052706</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -16560,11 +16560,11 @@
         </is>
       </c>
       <c r="J221">
-        <v>216</v>
+        <v>591</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485503</t>
+          <t xml:space="preserve">311520638</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-04</t>
+          <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -16616,7 +16616,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 57A</t>
+          <t xml:space="preserve">Åstræde 1</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -16626,7 +16626,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029205</t>
+          <t xml:space="preserve">8864464</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -16635,11 +16635,11 @@
         </is>
       </c>
       <c r="J222">
-        <v>214</v>
+        <v>913</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485504</t>
+          <t xml:space="preserve">311520617</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -16649,7 +16649,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-04</t>
+          <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16691,7 +16691,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 59A</t>
+          <t xml:space="preserve">Rævehøjparken 1</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -16701,7 +16701,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029206</t>
+          <t xml:space="preserve">212522, 100645398, 100645399, 100645400, 100645401, 100645402, 100645403, 100645404, 100645405, 100645406, 100645407, 100645408, 100645409, 100645410, 100645411, 100645412, 100645413, 100645414, 100645415, 100645416, 100645417, 100645418, 100645419, 100645420, 100645421, 100645422, 100645423, 100645424, 100645425, 100645426, 100645427</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -16710,21 +16710,21 @@
         </is>
       </c>
       <c r="J223">
-        <v>214</v>
+        <v>1848</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485505</t>
+          <t xml:space="preserve">311534879</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-04</t>
+          <t xml:space="preserve">2031-07-09</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16766,7 +16766,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Lundtoftevej 6</t>
+          <t xml:space="preserve">Rævehøjparken 11</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -16776,30 +16776,30 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030472</t>
+          <t xml:space="preserve">100645428, 100645429, 100645430, 100645431, 100645432, 100645433, 100645434, 100645435, 100645436, 100645437, 100645438, 100645439, 100645440, 100645441, 100645442, 100645443, 100645444, 100645445, 100645446, 100645447, 100645448, 100645449, 100645450, 100645451, 100645452, 100645453, 100645454, 100645455, 100645456, 100645457</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J224">
-        <v>84</v>
+        <v>1848</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311520616</t>
+          <t xml:space="preserve">311534879</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-17</t>
+          <t xml:space="preserve">2031-07-09</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16841,7 +16841,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby Hovedgade 1C</t>
+          <t xml:space="preserve">Rævehøjparken 2</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -16851,30 +16851,30 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052706</t>
+          <t xml:space="preserve">100645397, 100645461, 100645462, 100645464, 100645465, 100645466, 100645469, 100645471, 100645473, 100645474, 100645475, 100645476, 100645477, 100645479, 100645481, 100645482, 100645483, 100645484, 100645485, 100645487, 100645458, 100645459, 100645460, 100645463, 100645467, 100645468, 100645470, 100645472, 100645478, 100645480, 100645486</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J225">
-        <v>591</v>
+        <v>1850</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311520638</t>
+          <t xml:space="preserve">311534879</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-17</t>
+          <t xml:space="preserve">2031-07-09</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16916,7 +16916,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åstræde 1</t>
+          <t xml:space="preserve">Høstvej 12</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864464</t>
+          <t xml:space="preserve">2029365</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -16935,21 +16935,21 @@
         </is>
       </c>
       <c r="J226">
-        <v>913</v>
+        <v>386</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311520617</t>
+          <t xml:space="preserve">311569627</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-17</t>
+          <t xml:space="preserve">2031-12-22</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16991,7 +16991,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rævehøjparken 1</t>
+          <t xml:space="preserve">Høstvej 14</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -17001,30 +17001,30 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">212522, 100645398, 100645399, 100645400, 100645401, 100645402, 100645403, 100645404, 100645405, 100645406, 100645407, 100645408, 100645409, 100645410, 100645411, 100645412, 100645413, 100645414, 100645415, 100645416, 100645417, 100645418, 100645419, 100645420, 100645421, 100645422, 100645423, 100645424, 100645425, 100645426, 100645427</t>
+          <t xml:space="preserve">2029365</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J227">
-        <v>1848</v>
+        <v>566</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534879</t>
+          <t xml:space="preserve">311569627</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-09</t>
+          <t xml:space="preserve">2031-12-22</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -17051,12 +17051,12 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
+          <t xml:space="preserve">Lyngby almennyttige Boligselskab</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -17066,40 +17066,40 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rævehøjparken 11</t>
+          <t xml:space="preserve">Virumvej 127</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">100645428, 100645429, 100645430, 100645431, 100645432, 100645433, 100645434, 100645435, 100645436, 100645437, 100645438, 100645439, 100645440, 100645441, 100645442, 100645443, 100645444, 100645445, 100645446, 100645447, 100645448, 100645449, 100645450, 100645451, 100645452, 100645453, 100645454, 100645455, 100645456, 100645457</t>
+          <t xml:space="preserve">212323, 212324</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J228">
-        <v>1848</v>
+        <v>2065</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534879</t>
+          <t xml:space="preserve">311571303</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-09</t>
+          <t xml:space="preserve">2032-01-07</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -17126,12 +17126,12 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
+          <t xml:space="preserve">Lyngby almennyttige Boligselskab</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -17141,40 +17141,40 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rævehøjparken 2</t>
+          <t xml:space="preserve">Virumvej 123</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">100645397, 100645461, 100645462, 100645464, 100645465, 100645466, 100645469, 100645471, 100645473, 100645474, 100645475, 100645476, 100645477, 100645479, 100645481, 100645482, 100645483, 100645484, 100645485, 100645487, 100645458, 100645459, 100645460, 100645463, 100645467, 100645468, 100645470, 100645472, 100645478, 100645480, 100645486</t>
+          <t xml:space="preserve">414123, 414124</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J229">
-        <v>1850</v>
+        <v>2349</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534879</t>
+          <t xml:space="preserve">311571532</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-09</t>
+          <t xml:space="preserve">2032-01-10</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -17201,12 +17201,12 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
+          <t xml:space="preserve">Lyngby almennyttige Boligselskab</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -17216,17 +17216,17 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høstvej 12</t>
+          <t xml:space="preserve">Sennepsmarken 1</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029365</t>
+          <t xml:space="preserve">214823, 214825, 214824, 214826</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -17235,21 +17235,21 @@
         </is>
       </c>
       <c r="J230">
-        <v>386</v>
+        <v>5774</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569627</t>
+          <t xml:space="preserve">311576205</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-22</t>
+          <t xml:space="preserve">2032-02-02</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -17276,12 +17276,12 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
+          <t xml:space="preserve">LYNGBY BOLIGSELSKAB</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høstvej 14</t>
+          <t xml:space="preserve">Bauneporten 22</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -17301,30 +17301,30 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029365</t>
+          <t xml:space="preserve">205789, 205790</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J231">
-        <v>566</v>
+        <v>2207</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569627</t>
+          <t xml:space="preserve">311605065</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-22</t>
+          <t xml:space="preserve">2032-06-02</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -17351,12 +17351,12 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby almennyttige Boligselskab</t>
+          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -17366,17 +17366,17 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Virumvej 127</t>
+          <t xml:space="preserve">Asylgade 9A</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">212323, 212324</t>
+          <t xml:space="preserve">1300767</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -17385,21 +17385,21 @@
         </is>
       </c>
       <c r="J232">
-        <v>2065</v>
+        <v>940</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571303</t>
+          <t xml:space="preserve">311609045</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-07</t>
+          <t xml:space="preserve">2032-06-20</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -17426,12 +17426,12 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby almennyttige Boligselskab</t>
+          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -17441,17 +17441,17 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Virumvej 123</t>
+          <t xml:space="preserve">Emil Pipers Vej 5</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">414123, 414124</t>
+          <t xml:space="preserve">2064737</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -17460,21 +17460,21 @@
         </is>
       </c>
       <c r="J233">
-        <v>2349</v>
+        <v>1173</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571532</t>
+          <t xml:space="preserve">311609052</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-10</t>
+          <t xml:space="preserve">2032-06-20</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -17501,12 +17501,12 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby almennyttige Boligselskab</t>
+          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -17516,17 +17516,17 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sennepsmarken 1</t>
+          <t xml:space="preserve">Baunehøjvej 6</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">214823, 214825, 214824, 214826</t>
+          <t xml:space="preserve">2029257</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -17535,21 +17535,21 @@
         </is>
       </c>
       <c r="J234">
-        <v>5774</v>
+        <v>1110</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311576205</t>
+          <t xml:space="preserve">311614560</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-02</t>
+          <t xml:space="preserve">2032-07-11</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -17576,12 +17576,12 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t xml:space="preserve">LYNGBY BOLIGSELSKAB</t>
+          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -17591,7 +17591,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bauneporten 22</t>
+          <t xml:space="preserve">Carlshøjvej 7</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -17601,7 +17601,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">205789, 205790</t>
+          <t xml:space="preserve">2029261</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -17610,21 +17610,21 @@
         </is>
       </c>
       <c r="J235">
-        <v>2207</v>
+        <v>1908</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311605065</t>
+          <t xml:space="preserve">311614576</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-02</t>
+          <t xml:space="preserve">2032-07-11</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -17666,7 +17666,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asylgade 9A</t>
+          <t xml:space="preserve">Kastanievej 4A</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300767</t>
+          <t xml:space="preserve">2030205</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -17685,11 +17685,11 @@
         </is>
       </c>
       <c r="J236">
-        <v>940</v>
+        <v>1512</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311609045</t>
+          <t xml:space="preserve">311614565</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-20</t>
+          <t xml:space="preserve">2032-07-11</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17741,7 +17741,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emil Pipers Vej 5</t>
+          <t xml:space="preserve">Melagervej 1</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2064737</t>
+          <t xml:space="preserve">2029397</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -17760,11 +17760,11 @@
         </is>
       </c>
       <c r="J237">
-        <v>1173</v>
+        <v>328</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311609052</t>
+          <t xml:space="preserve">311614555</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -17774,7 +17774,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-20</t>
+          <t xml:space="preserve">2032-07-11</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunehøjvej 6</t>
+          <t xml:space="preserve">Melagervej 13</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -17826,20 +17826,20 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029257</t>
+          <t xml:space="preserve">2029397</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J238">
-        <v>1110</v>
+        <v>656</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614560</t>
+          <t xml:space="preserve">311614555</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -17891,7 +17891,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carlshøjvej 7</t>
+          <t xml:space="preserve">Melagervej 21</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -17901,20 +17901,20 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029261</t>
+          <t xml:space="preserve">2029397</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J239">
-        <v>1908</v>
+        <v>656</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614576</t>
+          <t xml:space="preserve">311614555</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanievej 4A</t>
+          <t xml:space="preserve">Melagervej 5</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -17976,20 +17976,20 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030205</t>
+          <t xml:space="preserve">2029397</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J240">
-        <v>1512</v>
+        <v>656</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614565</t>
+          <t xml:space="preserve">311614555</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -18041,7 +18041,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melagervej 1</t>
+          <t xml:space="preserve">Rønne Alle 2</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -18051,7 +18051,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029397</t>
+          <t xml:space="preserve">2063646</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -18060,11 +18060,11 @@
         </is>
       </c>
       <c r="J241">
-        <v>328</v>
+        <v>1968</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614555</t>
+          <t xml:space="preserve">311614558</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -18116,30 +18116,30 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melagervej 13</t>
+          <t xml:space="preserve">Furesøvej 161</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029397</t>
+          <t xml:space="preserve">1301632</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J242">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614555</t>
+          <t xml:space="preserve">311618189</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -18149,7 +18149,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-11</t>
+          <t xml:space="preserve">2032-08-02</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -18191,30 +18191,30 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melagervej 21</t>
+          <t xml:space="preserve">Furesøvej 163</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029397</t>
+          <t xml:space="preserve">1301632</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J243">
-        <v>656</v>
+        <v>291</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614555</t>
+          <t xml:space="preserve">311618186</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -18224,7 +18224,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-11</t>
+          <t xml:space="preserve">2032-08-02</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -18251,12 +18251,12 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
+          <t xml:space="preserve">Lyngby almennyttige Boligselskab</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -18266,7 +18266,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melagervej 5</t>
+          <t xml:space="preserve">Bredebovej 5</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -18276,30 +18276,30 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029397</t>
+          <t xml:space="preserve">203683, 203684</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J244">
-        <v>656</v>
+        <v>14925</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614555</t>
+          <t xml:space="preserve">311626375</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-11</t>
+          <t xml:space="preserve">2032-09-08</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -18341,7 +18341,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rønne Alle 2</t>
+          <t xml:space="preserve">Lyngby Kirkestræde 8B</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -18351,7 +18351,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2063646</t>
+          <t xml:space="preserve">2030014</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -18360,11 +18360,11 @@
         </is>
       </c>
       <c r="J245">
-        <v>1968</v>
+        <v>448</v>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614558</t>
+          <t xml:space="preserve">311628911</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -18374,7 +18374,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-11</t>
+          <t xml:space="preserve">2032-09-19</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -18416,17 +18416,17 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Furesøvej 161</t>
+          <t xml:space="preserve">Hjortholmsvej 7</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301632</t>
+          <t xml:space="preserve">2028658</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -18435,21 +18435,21 @@
         </is>
       </c>
       <c r="J246">
-        <v>552</v>
+        <v>306</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311618189</t>
+          <t xml:space="preserve">311646859</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">TT-Energioptimering</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-02</t>
+          <t xml:space="preserve">2032-12-02</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -18491,17 +18491,17 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Furesøvej 163</t>
+          <t xml:space="preserve">Fuglevadsvej 47</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301632</t>
+          <t xml:space="preserve">1300682</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -18510,21 +18510,21 @@
         </is>
       </c>
       <c r="J247">
-        <v>291</v>
+        <v>66</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311618186</t>
+          <t xml:space="preserve">311657990</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-02</t>
+          <t xml:space="preserve">2033-02-03</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -18551,12 +18551,12 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby almennyttige Boligselskab</t>
+          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -18566,7 +18566,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredebovej 5</t>
+          <t xml:space="preserve">Firskovvej 41</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -18576,7 +18576,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">203683, 203684</t>
+          <t xml:space="preserve">10180201</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -18585,21 +18585,21 @@
         </is>
       </c>
       <c r="J248">
-        <v>14925</v>
+        <v>1556</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311626375</t>
+          <t xml:space="preserve">311665365</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-08</t>
+          <t xml:space="preserve">2033-03-09</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -18641,7 +18641,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby Kirkestræde 8B</t>
+          <t xml:space="preserve">Slotsvænget 23A</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -18651,7 +18651,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030014</t>
+          <t xml:space="preserve">8864457</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -18660,21 +18660,21 @@
         </is>
       </c>
       <c r="J249">
-        <v>448</v>
+        <v>1832</v>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311628911</t>
+          <t xml:space="preserve">311665366</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-19</t>
+          <t xml:space="preserve">2033-03-09</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -18716,17 +18716,17 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjortholmsvej 7</t>
+          <t xml:space="preserve">Grønnevej 248</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028658</t>
+          <t xml:space="preserve">2103431</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -18735,21 +18735,21 @@
         </is>
       </c>
       <c r="J250">
-        <v>306</v>
+        <v>138</v>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646859</t>
+          <t xml:space="preserve">311665965</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t xml:space="preserve">TT-Energioptimering</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-02</t>
+          <t xml:space="preserve">2033-03-13</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18791,7 +18791,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglevadsvej 47</t>
+          <t xml:space="preserve">Sorgenfrivej 21</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -18801,30 +18801,30 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300682</t>
+          <t xml:space="preserve">2029965</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J251">
-        <v>66</v>
+        <v>260</v>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657990</t>
+          <t xml:space="preserve">311665962</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-03</t>
+          <t xml:space="preserve">2033-03-13</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18851,12 +18851,12 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
+          <t xml:space="preserve">Velliv Ejendomsinvestering P/S</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Firskovvej 41</t>
+          <t xml:space="preserve">Eremitageparken 103</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -18876,30 +18876,30 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">10180201</t>
+          <t xml:space="preserve">204081, 204082, 204083, 204084, 204085, 204086, 204087, 204088, 204090, 204091, 204092, 204093, 204094, 204095, 204106, 204096, 204097, 204102, 204105, 204109, 204114, 204098, 204101, 204103, 204104, 204107, 204108, 204110, 204112, 204113, 204115, 204116, 204118, 204119, 204117, 204120, 204121, 204123, 204124, 204125, 204126, 204127, 204128</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J252">
-        <v>1556</v>
+        <v>3112</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665365</t>
+          <t xml:space="preserve">311721371</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-09</t>
+          <t xml:space="preserve">2033-11-10</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18926,12 +18926,12 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
+          <t xml:space="preserve">Velliv Ejendomsinvestering P/S</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -18941,7 +18941,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slotsvænget 23A</t>
+          <t xml:space="preserve">Eremitageparken 11</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -18951,7 +18951,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864457</t>
+          <t xml:space="preserve">204044, 211172, 211184, 211206, 204045, 204056, 210751, 211217, 211617, 211627, 211661, 212015, 212026, 212063, 204067, 204078, 204089, 204100, 204111, 204122, 204133, 210706, 210717, 210740, 211195, 211650, 212037, 212075, 212467, 210718, 210729, 210762, 210773, 210784, 211139, 211150, 211161, 211173, 211228, 211584, 211595, 211606, 211628, 211639, 212043, 212052, 212074, 212478, 212489, 212500</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -18960,21 +18960,21 @@
         </is>
       </c>
       <c r="J253">
-        <v>1832</v>
+        <v>3891</v>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665366</t>
+          <t xml:space="preserve">311721371</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energihuset Danmark ApS</t>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-09</t>
+          <t xml:space="preserve">2033-11-10</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -19001,12 +19001,12 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
+          <t xml:space="preserve">Velliv Ejendomsinvestering P/S</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -19016,40 +19016,40 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnevej 248</t>
+          <t xml:space="preserve">Eremitageparken 201</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2103431</t>
+          <t xml:space="preserve">210742, 210743, 210746, 210755, 210757, 210758, 210766, 210768, 210772, 210786, 210744, 210745, 210747, 210748, 210749, 210750, 210787, 210752, 210753, 210754, 210756, 210765, 210767, 210759, 210760, 210761, 210763, 210764, 210769, 210770, 210771, 210774, 210775, 210776, 210777, 210778, 210779, 210780, 210781, 210782, 210783, 210785, 210788, 210789</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J254">
-        <v>138</v>
+        <v>3112</v>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665965</t>
+          <t xml:space="preserve">311721371</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energihuset Danmark ApS</t>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-13</t>
+          <t xml:space="preserve">2033-11-10</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -19076,12 +19076,12 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
+          <t xml:space="preserve">Velliv Ejendomsinvestering P/S</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -19091,7 +19091,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sorgenfrivej 21</t>
+          <t xml:space="preserve">Eremitageparken 209</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -19101,30 +19101,30 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029965</t>
+          <t xml:space="preserve">210790, 210791, 210792, 211148, 211159, 211170, 211171, 210793, 211138, 211140, 211141, 211142, 211143, 211144, 211147, 211149, 211163, 211166, 211181, 211145, 211146, 211151, 211152, 211153, 211154, 211155, 211156, 211157, 211158, 211160, 211162, 211164, 211165, 211167, 211168, 211169, 211174, 211175, 211176, 211177, 211178, 211179, 211180, 211182</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J255">
-        <v>260</v>
+        <v>3112</v>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665962</t>
+          <t xml:space="preserve">311721371</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energihuset Danmark ApS</t>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-13</t>
+          <t xml:space="preserve">2033-11-10</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -19166,7 +19166,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eremitageparken 103</t>
+          <t xml:space="preserve">Eremitageparken 307</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -19176,12 +19176,12 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">204081, 204082, 204083, 204084, 204085, 204086, 204087, 204088, 204090, 204091, 204092, 204093, 204094, 204095, 204106, 204096, 204097, 204102, 204105, 204109, 204114, 204098, 204101, 204103, 204104, 204107, 204108, 204110, 204112, 204113, 204115, 204116, 204118, 204119, 204117, 204120, 204121, 204123, 204124, 204125, 204126, 204127, 204128</t>
+          <t xml:space="preserve">211578, 211579, 211580, 211592, 211603, 211581, 211591, 211598, 211602, 211609, 211621, 211582, 211583, 211585, 211586, 211587, 211588, 211589, 211590, 211593, 211594, 211596, 211597, 211599, 211600, 211601, 211604, 211605, 211607, 211608, 211610, 211611, 211612, 211613, 211614, 211615, 211616, 211618, 211619, 211620, 211622, 211623, 211625</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J256">
@@ -19241,7 +19241,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eremitageparken 11</t>
+          <t xml:space="preserve">Eremitageparken 317</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -19251,16 +19251,16 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">204044, 211172, 211184, 211206, 204045, 204056, 210751, 211217, 211617, 211627, 211661, 212015, 212026, 212063, 204067, 204078, 204089, 204100, 204111, 204122, 204133, 210706, 210717, 210740, 211195, 211650, 212037, 212075, 212467, 210718, 210729, 210762, 210773, 210784, 211139, 211150, 211161, 211173, 211228, 211584, 211595, 211606, 211628, 211639, 212043, 212052, 212074, 212478, 212489, 212500</t>
+          <t xml:space="preserve">211626, 211630, 211631, 211634, 211638, 211641, 211649, 211653, 211665, 211669, 211629, 211640, 211662, 211632, 211633, 211635, 211636, 211637, 211642, 211643, 211644, 211645, 211646, 211647, 211648, 211651, 211652, 211654, 211655, 211656, 211657, 211658, 211659, 211660, 211663, 211664, 211666, 211667, 211668, 211670</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="J257">
-        <v>3891</v>
+        <v>3112</v>
       </c>
       <c r="K257" t="inlineStr">
         <is>
@@ -19301,12 +19301,12 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Velliv Ejendomsinvestering P/S</t>
+          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -19316,7 +19316,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eremitageparken 201</t>
+          <t xml:space="preserve">Eremitageparken 325</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -19326,16 +19326,16 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">210742, 210743, 210746, 210755, 210757, 210758, 210766, 210768, 210772, 210786, 210744, 210745, 210747, 210748, 210749, 210750, 210787, 210752, 210753, 210754, 210756, 210765, 210767, 210759, 210760, 210761, 210763, 210764, 210769, 210770, 210771, 210774, 210775, 210776, 210777, 210778, 210779, 210780, 210781, 210782, 210783, 210785, 210788, 210789</t>
+          <t xml:space="preserve">211671, 212016, 212017, 212018, 212019, 212020, 212021, 212022, 212023, 212024, 212025, 212027, 212028, 212029, 212030, 212031, 212032, 212033, 212034, 212035, 212036, 212039, 212038, 212040</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="J258">
-        <v>3112</v>
+        <v>1476</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Velliv Ejendomsinvestering P/S</t>
+          <t xml:space="preserve">Person med navne- og adressebeskyttelse</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -19391,7 +19391,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eremitageparken 209</t>
+          <t xml:space="preserve">Eremitageparken 361</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -19401,16 +19401,16 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">210790, 210791, 210792, 211148, 211159, 211170, 211171, 210793, 211138, 211140, 211141, 211142, 211143, 211144, 211147, 211149, 211163, 211166, 211181, 211145, 211146, 211151, 211152, 211153, 211154, 211155, 211156, 211157, 211158, 211160, 211162, 211164, 211165, 211167, 211168, 211169, 211174, 211175, 211176, 211177, 211178, 211179, 211180, 211182</t>
+          <t xml:space="preserve">212047, 212048, 212051, 212065, 212049, 212050, 212061, 212053, 212054, 212055, 212056, 212062, 212066, 212057, 212058, 212059, 212060, 212064, 212067, 212068, 212069, 212070, 212071, 212072</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="J259">
-        <v>3112</v>
+        <v>1476</v>
       </c>
       <c r="K259" t="inlineStr">
         <is>
@@ -19466,7 +19466,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eremitageparken 307</t>
+          <t xml:space="preserve">Eremitageparken 367</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -19476,16 +19476,16 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">211578, 211579, 211580, 211592, 211603, 211581, 211591, 211598, 211602, 211609, 211621, 211582, 211583, 211585, 211586, 211587, 211588, 211589, 211590, 211593, 211594, 211596, 211597, 211599, 211600, 211601, 211604, 211605, 211607, 211608, 211610, 211611, 211612, 211613, 211614, 211615, 211616, 211618, 211619, 211620, 211622, 211623, 211625</t>
+          <t xml:space="preserve">212073, 212076, 212087, 212091, 212098, 212102, 212109, 212453, 212077, 212078, 212079, 212080, 212081, 212082, 212083, 212084, 212085, 212088, 212089, 212094, 212096, 212101, 212103, 212443, 212451, 212454, 212460, 212090, 212092, 212093, 212095, 212099, 212100, 212104, 212105, 212106, 212107, 212444, 212445, 212446, 212447, 212448, 212449, 212450, 212455, 212456, 212457, 212458, 212459, 212461</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="J260">
-        <v>3112</v>
+        <v>3890</v>
       </c>
       <c r="K260" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eremitageparken 317</t>
+          <t xml:space="preserve">Eremitageparken 95</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -19551,12 +19551,12 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">211626, 211630, 211631, 211634, 211638, 211641, 211649, 211653, 211665, 211669, 211629, 211640, 211662, 211632, 211633, 211635, 211636, 211637, 211642, 211643, 211644, 211645, 211646, 211647, 211648, 211651, 211652, 211654, 211655, 211656, 211657, 211658, 211659, 211660, 211663, 211664, 211666, 211667, 211668, 211670</t>
+          <t xml:space="preserve">204046, 204047, 212498, 204048, 204049, 204050, 204065, 212505, 212510, 204051, 204052, 204053, 204054, 204055, 204057, 204058, 204059, 204060, 204061, 204062, 204063, 204064, 204066, 204068, 204069, 204070, 204071, 212509, 204072, 204073, 204074, 204075, 204076, 204077, 204079, 204080, 212499, 212501, 212502, 212503, 212504, 212506, 212507, 212508</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J261">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eremitageparken 325</t>
+          <t xml:space="preserve">Nøjsomhedsvej 1</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -19626,30 +19626,30 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">211671, 212016, 212017, 212018, 212019, 212020, 212021, 212022, 212023, 212024, 212025, 212027, 212028, 212029, 212030, 212031, 212032, 212033, 212034, 212035, 212036, 212039, 212038, 212040</t>
+          <t xml:space="preserve">2061486</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J262">
-        <v>1476</v>
+        <v>623</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311721371</t>
+          <t xml:space="preserve">311725677</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">Dansk Energi Management</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-10</t>
+          <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -19676,12 +19676,12 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Person med navne- og adressebeskyttelse</t>
+          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -19691,7 +19691,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eremitageparken 361</t>
+          <t xml:space="preserve">Nøjsomhedsvej 1</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -19701,30 +19701,30 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">212047, 212048, 212051, 212065, 212049, 212050, 212061, 212053, 212054, 212055, 212056, 212062, 212066, 212057, 212058, 212059, 212060, 212064, 212067, 212068, 212069, 212070, 212071, 212072</t>
+          <t xml:space="preserve">2061486</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J263">
-        <v>1476</v>
+        <v>3933</v>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311721371</t>
+          <t xml:space="preserve">311726115</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">Dansk Energi Management</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-10</t>
+          <t xml:space="preserve">2033-12-01</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -19751,12 +19751,12 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Velliv Ejendomsinvestering P/S</t>
+          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eremitageparken 367</t>
+          <t xml:space="preserve">Nøjsomhedsvej 1</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -19776,30 +19776,30 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">212073, 212076, 212087, 212091, 212098, 212102, 212109, 212453, 212077, 212078, 212079, 212080, 212081, 212082, 212083, 212084, 212085, 212088, 212089, 212094, 212096, 212101, 212103, 212443, 212451, 212454, 212460, 212090, 212092, 212093, 212095, 212099, 212100, 212104, 212105, 212106, 212107, 212444, 212445, 212446, 212447, 212448, 212449, 212450, 212455, 212456, 212457, 212458, 212459, 212461</t>
+          <t xml:space="preserve">2061486</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J264">
-        <v>3890</v>
+        <v>1086</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311721371</t>
+          <t xml:space="preserve">311726115</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">Dansk Energi Management</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-10</t>
+          <t xml:space="preserve">2033-12-01</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -19826,12 +19826,12 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Velliv Ejendomsinvestering P/S</t>
+          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eremitageparken 95</t>
+          <t xml:space="preserve">Nøjsomhedsvej 1</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -19851,30 +19851,30 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">204046, 204047, 212498, 204048, 204049, 204050, 204065, 212505, 212510, 204051, 204052, 204053, 204054, 204055, 204057, 204058, 204059, 204060, 204061, 204062, 204063, 204064, 204066, 204068, 204069, 204070, 204071, 212509, 204072, 204073, 204074, 204075, 204076, 204077, 204079, 204080, 212499, 212501, 212502, 212503, 212504, 212506, 212507, 212508</t>
+          <t xml:space="preserve">2061486</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J265">
-        <v>3112</v>
+        <v>935</v>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311721371</t>
+          <t xml:space="preserve">311726115</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">Dansk Energi Management</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-10</t>
+          <t xml:space="preserve">2033-12-01</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19901,12 +19901,12 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
+          <t xml:space="preserve">Naturstyrelsen</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -19916,40 +19916,40 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nøjsomhedsvej 1</t>
+          <t xml:space="preserve">Trepilevej 9</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2930</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2061486</t>
+          <t xml:space="preserve">715209, 9166715</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">581</t>
         </is>
       </c>
       <c r="J266">
-        <v>623</v>
+        <v>284</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725677</t>
+          <t xml:space="preserve">311800045</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Energi Management</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-29</t>
+          <t xml:space="preserve">2034-11-28</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nøjsomhedsvej 1</t>
+          <t xml:space="preserve">Toftebæksvej 3A</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -20001,7 +20001,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2061486</t>
+          <t xml:space="preserve">1300781</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -20010,21 +20010,21 @@
         </is>
       </c>
       <c r="J267">
-        <v>3933</v>
+        <v>480</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726115</t>
+          <t xml:space="preserve">311811264</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Energi Management</t>
+          <t xml:space="preserve">Fried-Energi ApS</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-01</t>
+          <t xml:space="preserve">2035-02-12</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -20066,7 +20066,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nøjsomhedsvej 1</t>
+          <t xml:space="preserve">Klintevej 14</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -20076,30 +20076,30 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2061486</t>
+          <t xml:space="preserve">2065128</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J268">
-        <v>1086</v>
+        <v>372</v>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726115</t>
+          <t xml:space="preserve">311824399</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Energi Management</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-01</t>
+          <t xml:space="preserve">2035-04-10</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -20141,7 +20141,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nøjsomhedsvej 1</t>
+          <t xml:space="preserve">Nøjsomhedsvej 6</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -20151,30 +20151,30 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2061486</t>
+          <t xml:space="preserve">2060670</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J269">
-        <v>935</v>
+        <v>119</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726115</t>
+          <t xml:space="preserve">311830616</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Energi Management</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-01</t>
+          <t xml:space="preserve">2035-05-09</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -20201,12 +20201,12 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturstyrelsen</t>
+          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -20216,40 +20216,40 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trepilevej 9</t>
+          <t xml:space="preserve">Nøjsomhedsvej 6</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">715209, 9166715</t>
+          <t xml:space="preserve">2060670</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">581</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J270">
-        <v>284</v>
+        <v>172</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800045</t>
+          <t xml:space="preserve">311830616</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-28</t>
+          <t xml:space="preserve">2035-05-09</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -20291,7 +20291,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftebæksvej 3A</t>
+          <t xml:space="preserve">Christian X's Alle 117</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -20301,30 +20301,30 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300781</t>
+          <t xml:space="preserve">2064948</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J271">
-        <v>480</v>
+        <v>560</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t xml:space="preserve">311811264</t>
+          <t xml:space="preserve">311862495</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fried-Energi ApS</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-12</t>
+          <t xml:space="preserve">2035-10-16</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -20366,7 +20366,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klintevej 14</t>
+          <t xml:space="preserve">Christian X's Alle 117</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -20376,30 +20376,30 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2065128</t>
+          <t xml:space="preserve">2064948</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J272">
-        <v>372</v>
+        <v>705</v>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t xml:space="preserve">311824399</t>
+          <t xml:space="preserve">311862485</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-10</t>
+          <t xml:space="preserve">2035-10-16</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -20441,7 +20441,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nøjsomhedsvej 6</t>
+          <t xml:space="preserve">Engelsborgvej 66</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -20451,20 +20451,20 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2060670</t>
+          <t xml:space="preserve">2064948</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J273">
-        <v>119</v>
+        <v>1047</v>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">311830616</t>
+          <t xml:space="preserve">311862497</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -20474,7 +20474,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-09</t>
+          <t xml:space="preserve">2035-10-16</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -20516,7 +20516,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nøjsomhedsvej 6</t>
+          <t xml:space="preserve">Engelsborgvej 66</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -20526,20 +20526,20 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2060670</t>
+          <t xml:space="preserve">2064948</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J274">
-        <v>172</v>
+        <v>1054</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">311830616</t>
+          <t xml:space="preserve">311862490</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -20549,7 +20549,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-09</t>
+          <t xml:space="preserve">2035-10-16</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -20591,7 +20591,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian X's Alle 117</t>
+          <t xml:space="preserve">Gammel Bagsværdvej 41</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -20606,15 +20606,15 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J275">
-        <v>560</v>
+        <v>257</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t xml:space="preserve">311862495</t>
+          <t xml:space="preserve">311862494</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -20666,7 +20666,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian X's Alle 117</t>
+          <t xml:space="preserve">Kongevejen 51</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -20676,30 +20676,30 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2064948</t>
+          <t xml:space="preserve">2027998</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J276">
-        <v>705</v>
+        <v>366</v>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t xml:space="preserve">311862485</t>
+          <t xml:space="preserve">311907609</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">B.F. Byggeservice ApS</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-16</t>
+          <t xml:space="preserve">2036-06-11</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -20741,40 +20741,40 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engelsborgvej 66</t>
+          <t xml:space="preserve">Kongsvænget 10</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2064948</t>
+          <t xml:space="preserve">2030815</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J277">
-        <v>1047</v>
+        <v>3540</v>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t xml:space="preserve">311862497</t>
+          <t xml:space="preserve">311926685</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-16</t>
+          <t xml:space="preserve">2036-09-18</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -20816,40 +20816,40 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engelsborgvej 66</t>
+          <t xml:space="preserve">Kongsvænget 10</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2064948</t>
+          <t xml:space="preserve">2030815</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J278">
-        <v>1054</v>
+        <v>428</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t xml:space="preserve">311862490</t>
+          <t xml:space="preserve">311926685</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-16</t>
+          <t xml:space="preserve">2036-09-18</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -20891,40 +20891,40 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Bagsværdvej 41</t>
+          <t xml:space="preserve">Kongsvænget 10</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2064948</t>
+          <t xml:space="preserve">2030815</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J279">
-        <v>257</v>
+        <v>431</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t xml:space="preserve">311862494</t>
+          <t xml:space="preserve">311926685</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-16</t>
+          <t xml:space="preserve">2036-09-18</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20966,7 +20966,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevejen 51</t>
+          <t xml:space="preserve">Nøjsomhedsvej 30</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -20976,7 +20976,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027998</t>
+          <t xml:space="preserve">2060987</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -20985,21 +20985,21 @@
         </is>
       </c>
       <c r="J280">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t xml:space="preserve">311907609</t>
+          <t xml:space="preserve">311926684</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.F. Byggeservice ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-11</t>
+          <t xml:space="preserve">2036-09-18</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">

--- a/public/exports-from-60-with-coowners/11715311.xlsx
+++ b/public/exports-from-60-with-coowners/11715311.xlsx
@@ -5089,7 +5089,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311017836</t>
+          <t xml:space="preserve">311017829</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
